--- a/diseases/d131/2026-2029.xlsx
+++ b/diseases/d131/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3292,6 +3377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3530,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3588,6 +3683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3884,6 +3989,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4029,6 +4139,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4174,6 +4289,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4319,6 +4439,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4464,6 +4589,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4609,6 +4739,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4754,6 +4889,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4899,6 +5039,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5042,6 +5187,11 @@
       <c r="S31" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">

--- a/diseases/d131/2026-2029.xlsx
+++ b/diseases/d131/2026-2029.xlsx
@@ -1836,9 +1836,6 @@
       <c r="O9" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -2754,9 +2751,6 @@
       <c r="O15" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -3519,9 +3513,6 @@
       <c r="O20" t="n">
         <v>1</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -3671,9 +3662,6 @@
       </c>
       <c r="O21" t="n">
         <v>1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0.0002865038132769385</v>

--- a/diseases/d131/2026-2029.xlsx
+++ b/diseases/d131/2026-2029.xlsx
@@ -765,17 +765,15 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -788,22 +786,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -918,17 +906,15 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -941,22 +927,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1071,17 +1047,15 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1094,22 +1068,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1224,17 +1188,15 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1247,22 +1209,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1377,17 +1329,15 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1400,22 +1350,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1530,17 +1470,15 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1553,22 +1491,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1683,17 +1611,15 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1706,22 +1632,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1836,14 +1752,12 @@
       <c r="O9" t="n">
         <v>1</v>
       </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
       <c r="R9" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1856,22 +1770,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1986,17 +1890,15 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2009,22 +1911,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2139,17 +2031,15 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2162,22 +2052,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2292,17 +2172,15 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2315,22 +2193,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2445,17 +2313,15 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2468,22 +2334,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2598,17 +2454,15 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2621,22 +2475,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2751,14 +2595,12 @@
       <c r="O15" t="n">
         <v>1</v>
       </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
       <c r="R15" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2771,22 +2613,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2901,17 +2733,15 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2924,22 +2754,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3054,17 +2874,15 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3077,22 +2895,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3207,17 +3015,15 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3230,22 +3036,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3360,17 +3156,15 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3383,22 +3177,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3513,14 +3297,12 @@
       <c r="O20" t="n">
         <v>1</v>
       </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
       <c r="R20" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3533,22 +3315,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3663,14 +3435,12 @@
       <c r="O21" t="n">
         <v>1</v>
       </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
       <c r="R21" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3683,22 +3453,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3813,17 +3573,15 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3836,22 +3594,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3966,17 +3714,15 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3989,22 +3735,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4119,14 +3855,12 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4139,22 +3873,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4269,14 +3993,12 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4289,22 +4011,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4419,14 +4131,12 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4439,22 +4149,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4569,14 +4269,12 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4589,22 +4287,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4719,14 +4407,12 @@
       <c r="O28" t="n">
         <v>1</v>
       </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
       <c r="R28" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4739,22 +4425,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4869,14 +4545,12 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4889,22 +4563,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5019,14 +4683,12 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5039,22 +4701,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5169,14 +4821,12 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5189,22 +4839,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
